--- a/temp/BBVA_VISA_20250328.xlsx
+++ b/temp/BBVA_VISA_20250328.xlsx
@@ -471,12 +471,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>-1549449.84</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-1549449,84</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -496,12 +498,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>41937.01</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>41937,01</t>
+        </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -521,12 +525,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>14234</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>14234,0</t>
+        </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -546,12 +552,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>850</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>850,0</t>
+        </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -571,12 +579,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>18255.35</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>18255,35</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -596,12 +606,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>4517.5</v>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>4517,5</t>
+        </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -621,12 +633,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>9999</v>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>9999,0</t>
+        </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -646,12 +660,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v>715.4</v>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>715,4</t>
+        </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -671,12 +687,14 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>3</v>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>3,0</t>
+        </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -696,12 +714,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D11" t="n">
-        <v>25620</v>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>25620,0</t>
+        </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -721,12 +741,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D12" t="n">
-        <v>249600</v>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>249600,0</t>
+        </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -746,12 +768,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>19800</v>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>19800,0</t>
+        </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -771,12 +795,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>5100</v>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>5100,0</t>
+        </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -796,12 +822,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>34000</v>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>34000,0</t>
+        </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -821,12 +849,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>43976.4</v>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>43976,4</t>
+        </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -846,12 +876,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D17" t="n">
-        <v>17735.5</v>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>17735,5</t>
+        </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -871,12 +903,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D18" t="n">
-        <v>13386.13</v>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>13386,13</t>
+        </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -896,12 +930,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D19" t="n">
-        <v>7136</v>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>7136,0</t>
+        </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -921,12 +957,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D20" t="n">
-        <v>3600</v>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>3600,0</t>
+        </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -946,12 +984,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D21" t="n">
-        <v>9270</v>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>9270,0</t>
+        </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -971,12 +1011,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D22" t="n">
-        <v>4760.3</v>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>4760,3</t>
+        </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -996,12 +1038,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D23" t="n">
-        <v>23750</v>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>23750,0</t>
+        </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1065,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D24" t="n">
-        <v>15905</v>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>15905,0</t>
+        </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1046,12 +1092,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D25" t="n">
-        <v>-1190.07</v>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>-1190,07</t>
+        </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1119,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D26" t="n">
-        <v>46571</v>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>46571,0</t>
+        </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1096,12 +1146,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D27" t="n">
-        <v>3890</v>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>3890,0</t>
+        </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1121,12 +1173,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D28" t="n">
-        <v>12411.05</v>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>12411,05</t>
+        </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1200,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D29" t="n">
-        <v>3299</v>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>3299,0</t>
+        </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1171,12 +1227,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D30" t="n">
-        <v>37400</v>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>37400,0</t>
+        </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1196,12 +1254,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D31" t="n">
-        <v>10800</v>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>10800,0</t>
+        </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1221,12 +1281,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D32" t="n">
-        <v>1500</v>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>1500,0</t>
+        </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1246,12 +1308,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D33" t="n">
-        <v>28730</v>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>28730,0</t>
+        </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1335,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D34" t="n">
-        <v>16415</v>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>16415,0</t>
+        </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1362,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D35" t="n">
-        <v>30950</v>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>30950,0</t>
+        </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1321,12 +1389,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D36" t="n">
-        <v>13625.79</v>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>13625,79</t>
+        </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1346,12 +1416,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D37" t="n">
-        <v>3479.21</v>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>3479,21</t>
+        </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1371,12 +1443,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D38" t="n">
-        <v>175000</v>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>175000,0</t>
+        </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1396,12 +1470,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D39" t="n">
-        <v>43995.01</v>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>43995,01</t>
+        </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1421,12 +1497,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D40" t="n">
-        <v>80106.7</v>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>80106,7</t>
+        </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1446,12 +1524,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D41" t="n">
-        <v>15670</v>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>15670,0</t>
+        </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1551,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D42" t="n">
-        <v>869</v>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>869,0</t>
+        </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1496,12 +1578,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D43" t="n">
-        <v>-304.15</v>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>-304,15</t>
+        </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1521,12 +1605,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D44" t="n">
-        <v>265.96</v>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>265,96</t>
+        </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1546,12 +1632,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D45" t="n">
-        <v>2792.58</v>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2792,58</t>
+        </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1571,12 +1659,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D46" t="n">
-        <v>5037.9</v>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>5037,9</t>
+        </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>

--- a/temp/BBVA_VISA_20250328.xlsx
+++ b/temp/BBVA_VISA_20250328.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>020396* PERSONAL FLOW 300060254971003</t>
+          <t>PERSONAL FLOW 300060254971003</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>041685K PEDIDOSYA RESTAURANTE</t>
+          <t>PEDIDOSYA RESTAURANTE</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>052966K PEDIDOSYA PROPINAS</t>
+          <t>PEDIDOSYA PROPINAS</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -571,7 +571,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>000001* EDENOR SA 000007691385963</t>
+          <t>EDENOR SA 000007691385963</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>550311* METROGAS SA DEB 040000136346</t>
+          <t>METROGAS SA DEB 040000136346</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>733781Q NETFLIX.COM ZMi3z4BSKUTmJH6gLd</t>
+          <t>NETFLIX.COM ZMi3z4BSKUTmJH6gLd</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -652,7 +652,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>000001* AUTOPISTAS URBAN 000000004488335</t>
+          <t>AUTOPISTAS URBAN 000000004488335</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>791406 OF USD 3,00</t>
+          <t>OF USD 3,00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>555152K MERPAGO*ELCLUBDELAMIL</t>
+          <t>MERPAGO*ELCLUBDELAMIL</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>615987K MERPAGO*ESCUELADAVINC</t>
+          <t>MERPAGO*ESCUELADAVINC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>007598* RAPPI</t>
+          <t>RAPPI</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>790792K MERPAGO*MINGYINGLIN</t>
+          <t>MERPAGO*MINGYINGLIN</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>035720* BARBERIA DORREGO</t>
+          <t>BARBERIA DORREGO</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>203813K MERPAGO*FARMACITY</t>
+          <t>MERPAGO*FARMACITY</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>192492K MERPAGO*FARMACITY</t>
+          <t>MERPAGO*FARMACITY</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>990727* BBVA SEGUROS A2052000420510-023-000</t>
+          <t>BBVA SEGUROS A2052000420510-023-000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>573299K MERPAGO*YPF</t>
+          <t>MERPAGO*YPF</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>008876* FARMACITY</t>
+          <t>FARMACITY</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>006105* UALA *MELANIE BELEN OST</t>
+          <t>UALA *MELANIE BELEN OST</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>009748K CABIFY25169EPTMFAA</t>
+          <t>CABIFY25169EPTMFAA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>009775* UALA *MELANIE BELEN OST</t>
+          <t>UALA *MELANIE BELEN OST</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>000800K PEDIDOSYA</t>
+          <t>PEDIDOSYA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>015296* TRIUNFO COOP D0000007681097-094-006</t>
+          <t>TRIUNFO COOP D0000007681097-094-006</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>008768* PAYU*AR*UBER</t>
+          <t>PAYU*AR*UBER</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>008457K AXION BONPLAND</t>
+          <t>AXION BONPLAND</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>246105V Spotify</t>
+          <t>Spotify</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>594463K MERPAGO*VILLACRESPO</t>
+          <t>MERPAGO*VILLACRESPO</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>005560* SANDRULI SRL</t>
+          <t>SANDRULI SRL</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>846976K PEDIDOSYA PROPINAS</t>
+          <t>PEDIDOSYA PROPINAS</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>001080K PEDIDOSYA</t>
+          <t>PEDIDOSYA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>000978K PEDIDOSYA</t>
+          <t>PEDIDOSYA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>001040K PEDIDOSYA</t>
+          <t>PEDIDOSYA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>120382* EXPERTA SEGURO0000034754103-015-005</t>
+          <t>EXPERTA SEGURO0000034754103-015-005</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>000001* AUBASA 960001911719401</t>
+          <t>AUBASA 960001911719401</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>152777K MERPAGO*UNIVERSOALEMA</t>
+          <t>MERPAGO*UNIVERSOALEMA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>043528* PERSONAL FLOW 300060254971003</t>
+          <t>PERSONAL FLOW 300060254971003</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>001811K VEA SM 700 MODO</t>
+          <t>VEA SM 700 MODO</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>709341K MERPAGO*SUPERDIA</t>
+          <t>MERPAGO*SUPERDIA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>007907* EMOVA SUBTE</t>
+          <t>EMOVA SUBTE</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
